--- a/src/rodos_corpus/data/corpus/rendered/finance/REESTR-PLAT-20260915.xlsx
+++ b/src/rodos_corpus/data/corpus/rendered/finance/REESTR-PLAT-20260915.xlsx
@@ -477,17 +477,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ЦМТ-2025/09</t>
+          <t>ВР-2026/03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ООО «Цветмет-Торг»</t>
+          <t>АО «Волга-Редуктор»</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>007712345001</t>
+          <t>006316445577</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -507,17 +507,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>РМ-2025/01</t>
+          <t>БМК-2025/11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>АО «Редмаш»</t>
+          <t>ООО «Балтмашкомплект»</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>005250778899</t>
+          <t>007806334455</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -537,17 +537,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ЛЛ-2025/05</t>
+          <t>ЦМТ-2025/09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ООО «Логистик-Лайн»</t>
+          <t>ООО «Цветмет-Торг»</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>006316112233</t>
+          <t>007712345001</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -567,17 +567,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>АТД-2025/06</t>
+          <t>РМ-2025/01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ООО «Агротех-Деталь»</t>
+          <t>АО «Редмаш»</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>005401667788</t>
+          <t>005250778899</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -597,17 +597,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>АЦ-2024/45</t>
+          <t>ЛЛ-2025/05</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ООО «Абразив-Центр»</t>
+          <t>ООО «Логистик-Лайн»</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>006452003311</t>
+          <t>006316112233</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -627,17 +627,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>СИЗ-2025/02</t>
+          <t>МТЦ-2025/10</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ООО «СИЗ-Профи»</t>
+          <t>ООО «Машторг-Центр»</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>007705998877</t>
+          <t>007743221100</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -657,17 +657,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ИТС-2025/16</t>
+          <t>АЦ-2024/45</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ООО «ИТ-Снаб-Партнёр»</t>
+          <t>ООО «Абразив-Центр»</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>007736445566</t>
+          <t>006452003311</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -687,17 +687,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ХР-2025/07</t>
+          <t>KMP-2025/02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ООО «Химресурс-Урал»</t>
+          <t>ТОО «KazMashParts»</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>005904445566</t>
+          <t>000000123456</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -717,17 +717,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>РСУ-2024/33</t>
+          <t>АТД-2025/06</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ООО «Ремсервис-Урал»</t>
+          <t>ООО «Агротех-Деталь»</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>006671889900</t>
+          <t>005401667788</t>
         </is>
       </c>
       <c r="D12" t="n">
